--- a/files/iso/DI-IMS-F-01_Rev00.xlsx
+++ b/files/iso/DI-IMS-F-01_Rev00.xlsx
@@ -55,8 +55,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'QF-02'!$A$1:$G$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'QF-03'!$13:$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'QF-03'!$A$1:$H$25</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'QF-04'!$12:$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'QF-04'!$A$1:$G$47</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'QF-04'!$11:$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'QF-04'!$A$1:$J$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'QF-05'!$A$1:$F$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'QF-06'!$A$1:$G$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'QF-06-1'!$12:$12</definedName>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>입고별·LOT별</t>
+          <t>입고별</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1999,22 +1999,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>부품 LOT 및 판넬 추적</t>
+          <t>판넬 LOT 및 출하 이력</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>생산관리</t>
+          <t>생산관리 / 품질</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>사용·교체·납품 시</t>
+          <t>판넬 출하·인수·AS 시</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.4, 5.7</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -5081,7 +5081,7 @@
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>프로젝트·판넬·LOT·공정</t>
+          <t>프로젝트·판넬 LOT·공정</t>
         </is>
       </c>
       <c r="F6" s="10" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>AS: 보증 판정·교체부품(QF-04)</t>
+          <t>AS: 보증 판정·교체부품(QF-04 이력)</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -10047,7 +10047,7 @@
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
+    <row r="28" ht="31.65" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>명판·표시</t>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>정격·제조번호·경고표시 내용</t>
+          <t>정격·제조번호(판넬 LOT)·경고표시 내용</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -10357,7 +10357,7 @@
     <row r="8" ht="26.3" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>고객이 요구하는 LOT 작업일지·공정이동표를 이 양식으로 연결한다. 배선·시험 작업자와 실적을 추적하고 불합격은 다음 단계로 인계하지 않는다. 판넬에 부착해 이동시키거나 ERP 공정 실적으로 대체할 수 있다.</t>
+          <t>고객이 요구하는 LOT 작업일지·공정이동표는 판넬 LOT(제조번호)별로 이 양식으로 연결한다. 배선·시험 작업자와 실적을 추적하고 불합격은 다음 단계로 인계하지 않는다. 판넬에 부착해 이동시키거나 ERP 공정 실적으로 대체할 수 있다.</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -10370,7 +10370,7 @@
       <c r="I8" s="2" t="n"/>
     </row>
     <row r="9" ht="5" customHeight="1"/>
-    <row r="10" ht="26" customHeight="1">
+    <row r="10" ht="31.65" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>공정</t>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>LOT/자재기록</t>
+          <t>자재기록(QF-03)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="31.65" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>입고·불출</t>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>QF-03 합격품만 불출, LOT 기록(QF-04)</t>
+          <t>QF-03 합격품만 불출 (부품은 LOT 없이 발주·입고번호로 연결)</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>이물 제거·이동부 고정·단자/개구부 보호·방습·명판/취급표시·팔레트 고정·동봉물(도면·키·예비품), 중량·인양점 확인 → PF-00 출하 승인</t>
+          <t>이물 제거·이동부 고정·단자/개구부 보호·방습·명판/취급표시·팔레트 고정·동봉물(도면·키·예비품), 중량·인양점 확인 → PF-00 출하 승인 → QF-04 출하 기록</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="31.65" customHeight="1">
+    <row r="8" ht="44.475" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>3</t>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>프로젝트 번호는 수주 시 영업관리가 부여한 번호(ERP 수주번호)를 모든 기록에 똑같이 씁니다. 판넬은 도면 Tag(예: LCP-01)와 제조번호(프로젝트번호-순번)를 함께 적고 제조번호를 명판에 표시합니다.</t>
+          <t>프로젝트 번호는 수주 시 영업관리가 부여한 번호(ERP 수주번호)를 모든 기록에 똑같이 씁니다. 판넬은 도면 Tag(예: LCP-01)와 제조번호(프로젝트번호-순번)를 함께 적고 제조번호를 명판에 표시합니다. LOT 번호는 출하 단위인 판넬에만 부여하며 제조번호가 곧 판넬 LOT입니다. 부품에는 LOT를 따로 매기지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>예시(실제 운영 기록 아님): 프로젝트 DI-EX-01 / 판넬 CP-01 / 입고 차단기 LOT ABC / QF-03 합격 → QF-04 설치위치 TB01 → QF-16 배선작업자·일자 → QF-05 숙련자 확인 → QF-06 실측값 → PF-00 품질 출하승인.</t>
+          <t>예시(실제 운영 기록 아님): 프로젝트 DI-EX-01 / 판넬 CP-01 (판넬 LOT DI-EX-01-01) / 입고 차단기 QF-03 합격 → QF-16 배선작업자·일자 → QF-05 숙련자 확인 → QF-06 실측값 → PF-00 품질 출하승인 → QF-04 출하일·납품처.</t>
         </is>
       </c>
     </row>
@@ -17170,7 +17170,7 @@
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
     </row>
-    <row r="17" ht="26" customHeight="1">
+    <row r="17" ht="31.65" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>제조·검사</t>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LOT·작업자·배선·FAT·교정·출하</t>
+          <t>판넬 LOT·작업자·배선·FAT·교정·출하</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>QF-10 승인 공급자 발주 / QF-03 판정 / QF-04 추적</t>
+          <t>QF-10 승인 공급자 발주 / QF-03 판정 (부품 LOT 미부여)</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -19958,7 +19958,7 @@
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
     </row>
-    <row r="22" ht="31.65" customHeight="1">
+    <row r="22" ht="44.475" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>출하</t>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>QF-06 합격 · 최종 PLC(QF-08) · 포장 확인(QF-16) · 출하 영향 NCR 종결 또는 고객 특채 서면</t>
+          <t>QF-06 합격 · 최종 PLC(QF-08) · 포장 확인(QF-16) · 출하 영향 NCR 종결 또는 고객 특채 서면 · 판넬 LOT 출하 기록(QF-04)</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -20588,7 +20588,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-03 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 품질 | 작성: 입고별·LOT별</t>
+          <t>동인엔시스 | DI-QF-03 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 품질 | 작성: 입고별</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -20676,7 +20676,7 @@
     <row r="10" ht="14.15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>주요 전기부품(인버터·PLC·차단기 등)·외함은 모델/수량/외관/시리얼·필수증명을 확인한다. 외함은 치수·가공·도장·접지점까지 확인한다. 소모품도 고객 지정·안전 중요·문제 발생 시 검사한다.</t>
+          <t>주요 전기부품(인버터·PLC·차단기 등)·외함은 모델·정격/수량/외관·필수 성적서를 확인한다. 외함은 치수·가공·도장·접지점까지 확인한다. 소모품도 고객 지정·안전 중요·문제 발생 시 검사한다.</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -20687,10 +20687,10 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
     </row>
-    <row r="11" ht="14.15" customHeight="1">
+    <row r="11" ht="26.3" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>합격품만 불출한다. 불합격·보류품은 '부적합' 표시 후 격리하고 QF-09로 처리한다. 고객 지급품은 소유자·수량·상태를 확인하고 손상 시 고객에 통보한다.</t>
+          <t>합격품만 불출한다. 불합격·보류품은 '부적합' 표시 후 격리하고 QF-09로 처리한다. 고객 지급품은 소유자·수량·상태를 확인하고 손상 시 고객에 통보한다. 부품에는 LOT 번호를 따로 매기지 않는다(LOT는 판넬에만, QF-04).</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>LOT/SN</t>
+          <t>적용 판넬 LOT</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -20930,23 +20930,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G47"/>
+  <dimension ref="A2:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.7" customWidth="1" min="1" max="1"/>
-    <col width="21.5" customWidth="1" min="2" max="2"/>
-    <col width="21.5" customWidth="1" min="3" max="3"/>
-    <col width="15.1" customWidth="1" min="4" max="4"/>
-    <col width="19.4" customWidth="1" min="5" max="5"/>
-    <col width="23.7" customWidth="1" min="6" max="6"/>
-    <col width="15.1" customWidth="1" min="7" max="7"/>
+    <col width="16.7" customWidth="1" min="1" max="1"/>
+    <col width="15.7" customWidth="1" min="2" max="2"/>
+    <col width="12.5" customWidth="1" min="3" max="3"/>
+    <col width="11.5" customWidth="1" min="4" max="4"/>
+    <col width="13.6" customWidth="1" min="5" max="5"/>
+    <col width="13.6" customWidth="1" min="6" max="6"/>
+    <col width="16.7" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="17.8" customWidth="1" min="9" max="9"/>
+    <col width="10.4" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1"/>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>부품 LOT 및 판넬 추적</t>
+          <t>판넬 LOT 및 출하 이력</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -20955,11 +20958,14 @@
       <c r="E2" s="1" t="n"/>
       <c r="F2" s="1" t="n"/>
       <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-04 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 | 작성: 사용·교체·납품 시</t>
+          <t>동인엔시스 | DI-QF-04 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 품질 | 작성: 판넬 출하·인수·AS 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -20968,6 +20974,9 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="20" customHeight="1">
@@ -20985,47 +20994,60 @@
       </c>
       <c r="E5" s="10" t="n"/>
       <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>프로젝트명·현장</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>판넬 번호(제조번호)</t>
+          <t>판넬 수량</t>
         </is>
       </c>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>납품처·납품일</t>
+          <t>작성자</t>
         </is>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>작성자</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>관련 QF-16 번호</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
-    </row>
-    <row r="8" ht="5" customHeight="1"/>
-    <row r="9" ht="14.15" customHeight="1">
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>품질 확인자</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="5" customHeight="1"/>
+    <row r="8" ht="26.3" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>LOT 번호는 출하 단위인 판넬에만 부여한다. 판넬 LOT = 제조번호(프로젝트번호-순번)이며 명판·QF-05·QF-06·QF-16·SF-02·출하서류에 같은 번호를 쓴다. 한 번 부여한 번호는 다시 쓰지 않는다. 배선 확인=QF-05, FAT=QF-06, 출하 승인=PF-00, SAT=QF-07, AS=QF-09.</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="26.3" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LOT → 입고 → 판넬 설치 위치 → 작업자·검사 → 납품처가 연결되어야 한다. 교체 이력은 지우지 않고 줄을 그어 남긴다.</t>
+          <t>부품에는 LOT 번호를 따로 매기지 않는다. 부품은 판넬 LOT → BOM(도면 Rev) → 입고 기록(QF-03 발주·입고번호)으로 거슬러 확인한다. 고객이 부품 시리얼 목록을 요구하면 비고에 첨부 경로를 적는다. AS 교체·변경은 지우지 않고 이력에 덧붙인다.</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -21034,59 +21056,76 @@
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="14.15" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>추적 대상: 인버터·PLC·차단기 등 주요품, 고객 지정품, 안전 관련 부품. BOM·ERP 출력본에 같은 열이 있으면 대체할 수 있다(PF-00에 경로 기록).</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="5" customHeight="1"/>
-    <row r="12" ht="31.65" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>부품·모델</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>LOT/시리얼</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>공급자·입고기록(QF-03)</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>도면 위치(Tag)</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>설치 작업자·일자(QF-16)</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>교체·변경 이력</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="5" customHeight="1"/>
+    <row r="11" ht="31.65" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>판넬 LOT (제조번호)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>도면 Tag·설명</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>도면 Rev / PLC</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>배선 확인일</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>FAT 판정·일자</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>출하 승인·일자</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>납품처·설치 위치</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>SAT·인수일</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>변경·AS 이력</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
@@ -21094,8 +21133,11 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
@@ -21103,8 +21145,11 @@
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
@@ -21112,8 +21157,11 @@
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
@@ -21121,8 +21169,11 @@
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
@@ -21130,8 +21181,11 @@
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
@@ -21139,8 +21193,11 @@
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
@@ -21148,8 +21205,11 @@
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
@@ -21157,8 +21217,11 @@
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
@@ -21166,8 +21229,11 @@
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="5" t="n"/>
@@ -21175,8 +21241,11 @@
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
@@ -21184,8 +21253,11 @@
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
@@ -21193,8 +21265,11 @@
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
@@ -21202,8 +21277,11 @@
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
@@ -21211,8 +21289,11 @@
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
@@ -21220,8 +21301,11 @@
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="n"/>
@@ -21229,8 +21313,11 @@
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
@@ -21238,8 +21325,11 @@
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="5" t="n"/>
@@ -21247,8 +21337,11 @@
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
@@ -21256,8 +21349,11 @@
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
@@ -21265,8 +21361,11 @@
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
@@ -21274,8 +21373,11 @@
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
@@ -21283,8 +21385,11 @@
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
@@ -21292,8 +21397,11 @@
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="26" customHeight="1">
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
@@ -21301,8 +21409,11 @@
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
@@ -21310,129 +21421,87 @@
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="6" customHeight="1"/>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>첨부·대체 기록 번호와 보관 경로 / 적용 제외(해당없음) 사유 / 미결 확인 :</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>작성</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>검토</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>승인</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="13" t="n"/>
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="9" t="inlineStr">
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>성명·서명</t>
         </is>
       </c>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="13" t="n"/>
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A8:J8"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="A45:C47"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A39:F41"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="E6:G6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/files/iso/DI-IMS-F-01_Rev00.xlsx
+++ b/files/iso/DI-IMS-F-01_Rev00.xlsx
@@ -1828,7 +1828,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-IMS-F-01 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일</t>
+          <t>동인엔시스 | DI-IMS-F-01 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1841,7 +1841,7 @@
     <row r="5" ht="14.15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>승인 전 운영기준안입니다. 원본 빈 양식은 보존하고 프로젝트별 사본으로 작성합니다. 실제 서명·결과·일자를 입력합니다.</t>
+          <t>2026.10.01 대표 승인·시행. 원본 빈 양식은 보존하고 프로젝트별 사본으로 작성합니다. 실제 서명·결과·일자를 입력합니다.</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -3124,7 +3124,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-06-1 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 시험 담당 / 품질 | 작성: FAT·SAT 점별 시험 시</t>
+          <t>동인엔시스 | DI-QF-06-1 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 시험 담당 / 품질 | 작성: FAT·SAT 점별 시험 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -4220,7 +4220,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-07 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 시운전 담당 / 품질 | 작성: 현장별·미결종결 시</t>
+          <t>동인엔시스 | DI-QF-07 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 시운전 담당 / 품질 | 작성: 현장별·미결종결 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -4658,7 +4658,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-08 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 프로그램 / 기술팀 총괄 | 작성: 변경·FAT·출하·SAT 종료 시</t>
+          <t>동인엔시스 | DI-QF-08 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 프로그램 / 기술팀 총괄 | 작성: 변경·FAT·출하·SAT 종료 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -5042,7 +5042,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-09 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 품질 / 안전·환경 담당 | 작성: 발견·사건·클레임 시</t>
+          <t>동인엔시스 | DI-QF-09 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 품질 / 안전·환경 담당 | 작성: 발견·사건·클레임 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -5455,7 +5455,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-10 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 품질 | 작성: 신규 발주 전·연 1회·중대한 문제 시</t>
+          <t>동인엔시스 | DI-QF-10 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 생산관리 / 품질 | 작성: 신규 발주 전·연 1회·중대한 문제 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -5969,7 +5969,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-11 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 품질 / 생산관리 | 작성: 등록·교정·사용 전·설비점검 시</t>
+          <t>동인엔시스 | DI-QF-11 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 품질 / 생산관리 | 작성: 등록·교정·사용 전·설비점검 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -6688,7 +6688,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-12 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 부서 책임자 / 안전 담당·품질 | 작성: 배치 전·변경 시·교육 실시 시</t>
+          <t>동인엔시스 | DI-QF-12 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 부서 책임자 / 안전 담당·품질 | 작성: 배치 전·변경 시·교육 실시 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -7490,7 +7490,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-13 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 품질 / 경영관리 | 작성: 개정·배포·보관경로 변경 시</t>
+          <t>동인엔시스 | DI-QF-13 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 품질 / 경영관리 | 작성: 개정·배포·보관경로 변경 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -8139,7 +8139,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-13-2 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 경영관리 / 품질 | 작성: 주 1회 백업 확인 / 월 1회 표본 복구</t>
+          <t>동인엔시스 | DI-QF-13-2 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 경영관리 / 품질 | 작성: 주 1회 백업 확인 / 월 1회 표본 복구</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -8931,7 +8931,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-14 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 영업관리 / 품질 | 작성: SAT 종료·연 1회·고객감사 시</t>
+          <t>동인엔시스 | DI-QF-14 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 영업관리 / 품질 | 작성: SAT 종료·연 1회·고객감사 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -9310,7 +9310,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-IMS-F-01 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일</t>
+          <t>동인엔시스 | DI-IMS-F-01 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -9375,7 +9375,11 @@
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026.10.01 대표이사</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="5" t="n"/>
@@ -9673,7 +9677,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-15 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 설계·시험 / 기술팀 총괄 | 작성: 출도·발주·제작 전 / 변경 시</t>
+          <t>동인엔시스 | DI-QF-15 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 설계·시험 / 기술팀 총괄 | 작성: 출도·발주·제작 전 / 변경 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -10294,7 +10298,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-16 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 제조 | 작성: 판넬별 단계 완료 시</t>
+          <t>동인엔시스 | DI-QF-16 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 생산관리 / 제조 | 작성: 판넬별 단계 완료 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -10709,7 +10713,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-01 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 왕리홍 대리 / 현장 근로자 | 작성: 최초·연 1회·변경·사고/아차사고 시</t>
+          <t>동인엔시스 | DI-SF-01 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리 / 현장 근로자 | 작성: 최초·연 1회·변경·사고/아차사고 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -11711,7 +11715,7 @@
     <row r="3" ht="26.3" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-02 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 작업 책임자 / 왕리홍 대리 | 작성: FAT/SAT 작업 시작·전원상태 변경·종료 시</t>
+          <t>동인엔시스 | DI-SF-02 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 작업 책임자 / 왕리홍 대리 | 작성: FAT/SAT 작업 시작·전원상태 변경·종료 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -12110,7 +12114,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-03 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 왕리홍 대리 | 작성: 외주 현장작업 시작 전·조건 변경 시</t>
+          <t>동인엔시스 | DI-SF-03 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 생산관리 / 왕리홍 대리 | 작성: 외주 현장작업 시작 전·조건 변경 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -12478,7 +12482,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-04 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 대표이사 / 경영관리 | 작성: 선임·변경 시 / 반기(6월·12월) 평가</t>
+          <t>동인엔시스 | DI-SF-04 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표이사 / 경영관리 | 작성: 선임·변경 시 / 반기(6월·12월) 평가</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -12924,7 +12928,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-05 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 왕리홍 대리 / 경영관리 | 작성: 매년 1월 계획 / 교육 실시 시 / 반기 실적 확인</t>
+          <t>동인엔시스 | DI-SF-05 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리 / 경영관리 | 작성: 매년 1월 계획 / 교육 실시 시 / 반기 실적 확인</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -13407,7 +13411,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-06 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 경영관리 / 왕리홍 대리 | 작성: 매년 1월 대상자 확정 / 수검 후 / 연 1회 유해인자 판정</t>
+          <t>동인엔시스 | DI-SF-06 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 경영관리 / 왕리홍 대리 | 작성: 매년 1월 대상자 확정 / 수검 후 / 연 1회 유해인자 판정</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -14005,7 +14009,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-07 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 대표이사 / 왕리홍 대리 / 경영관리 | 작성: 매년 1월 편성 / 분기 집행 확인 / 추가 필요 시</t>
+          <t>동인엔시스 | DI-SF-07 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표이사 / 왕리홍 대리 / 경영관리 | 작성: 매년 1월 편성 / 분기 집행 확인 / 추가 필요 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -14409,7 +14413,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-08 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 왕리홍 대리 / 대표이사 | 작성: 6월·12월(반기 1회) / 중대재해·중대한 변경 후 추가</t>
+          <t>동인엔시스 | DI-SF-08 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리 / 대표이사 | 작성: 6월·12월(반기 1회) / 중대재해·중대한 변경 후 추가</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -14826,7 +14830,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-IMS-F-01 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일</t>
+          <t>동인엔시스 | DI-IMS-F-01 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -15033,7 +15037,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-09 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 왕리홍 대리 | 작성: 신규 외주 선정 전 / 연 1회 / 사고·중대한 문제 시</t>
+          <t>동인엔시스 | DI-SF-09 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 생산관리 / 왕리홍 대리 | 작성: 신규 외주 선정 전 / 연 1회 / 사고·중대한 문제 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -15492,7 +15496,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-10 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 왕리홍 대리 / 대표이사 | 작성: 재해·중대한 아차사고 발생 즉시 / 조사 완료 시</t>
+          <t>동인엔시스 | DI-SF-10 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리 / 대표이사 | 작성: 재해·중대한 아차사고 발생 즉시 / 조사 완료 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -15949,7 +15953,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-EF-01 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 성문기 과장 | 작성: 최초·연 1회·변경 시</t>
+          <t>동인엔시스 | DI-EF-01 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 성문기 과장 | 작성: 최초·연 1회·변경 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -16979,7 +16983,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-01 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 품질 / 독립된 심사원 | 작성: 연 1회·중대한 변경/지적 시 추가</t>
+          <t>동인엔시스 | DI-MF-01 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 품질 / 독립된 심사원 | 작성: 연 1회·중대한 변경/지적 시 추가</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -17545,7 +17549,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-02 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 대표이사 / 품질 | 작성: 연 1회·중대한 변경 시</t>
+          <t>동인엔시스 | DI-MF-02 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표이사 / 품질 | 작성: 연 1회·중대한 변경 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -17950,7 +17954,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-03 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 대표 / 각 담당 | 작성: 연초·분기 실적·경영검토</t>
+          <t>동인엔시스 | DI-MF-03 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표 / 각 담당 | 작성: 연초·분기 실적·경영검토</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -18332,7 +18336,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-04 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 대표 / 품질·안전·환경 | 작성: 최초·연 1회·주요 변화 시</t>
+          <t>동인엔시스 | DI-MF-04 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표 / 품질·안전·환경 | 작성: 최초·연 1회·주요 변화 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -18720,7 +18724,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-05 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 왕리홍 대리·성문기 과장 / 품질 | 작성: 최초·변경 시·분기 최신성 확인·연 1회 평가</t>
+          <t>동인엔시스 | DI-MF-05 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리·성문기 과장 / 품질 | 작성: 최초·변경 시·분기 최신성 확인·연 1회 평가</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -19356,7 +19360,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-06 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 안전·환경 담당 | 작성: 월 1회 협의 / 연 1회 훈련 / 변경·실제 비상 후</t>
+          <t>동인엔시스 | DI-MF-06 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 안전·환경 담당 | 작성: 월 1회 협의 / 연 1회 훈련 / 변경·실제 비상 후</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -19678,7 +19682,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-PF-00 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 영업관리·품질 | 작성: 수주 전 / 단계 완료 시</t>
+          <t>동인엔시스 | DI-PF-00 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 영업관리·품질 | 작성: 수주 전 / 단계 완료 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -20151,7 +20155,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-02 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 설계·프로그램 / 기술팀 총괄 | 작성: 설계 착수·출도·변경 시</t>
+          <t>동인엔시스 | DI-QF-02 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 설계·프로그램 / 기술팀 총괄 | 작성: 설계 착수·출도·변경 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -20588,7 +20592,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-03 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 품질 | 작성: 입고별</t>
+          <t>동인엔시스 | DI-QF-03 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 생산관리 / 품질 | 작성: 입고별</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -20965,7 +20969,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-04 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 생산관리 / 품질 | 작성: 판넬 출하·인수·AS 시</t>
+          <t>동인엔시스 | DI-QF-04 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 생산관리 / 품질 | 작성: 판넬 출하·인수·AS 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -21552,7 +21556,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-05 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 제조 / 생산관리 | 작성: 판넬별 배선 완료·수정 후</t>
+          <t>동인엔시스 | DI-QF-05 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 제조 / 생산관리 | 작성: 판넬별 배선 완료·수정 후</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -21994,7 +21998,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-06 | Rev.00 | 제정 2026.10.01 | 시행일: 대표 승인일   ·   담당: 시험 담당 / 품질 | 작성: 판넬별 시험·재시험</t>
+          <t>동인엔시스 | DI-QF-06 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 시험 담당 / 품질 | 작성: 판넬별 시험·재시험</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
